--- a/backend/data/financials_by_company/000010.SZ.xlsx
+++ b/backend/data/financials_by_company/000010.SZ.xlsx
@@ -4153,10 +4153,8 @@
           <t>Shenzhen</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>518101</t>
-        </is>
+      <c r="D2" t="n">
+        <v>518101</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -4367,7 +4365,7 @@
         <v>-1697900</v>
       </c>
       <c r="BM2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
@@ -4630,7 +4628,7 @@
         <v>1619780340</v>
       </c>
       <c r="EH2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI2" t="inlineStr"/>
     </row>
